--- a/03_Source_To_Target_Mapping/RetailMart_STM.xlsx
+++ b/03_Source_To_Target_Mapping/RetailMart_STM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub_Projects\Retail_DWH_Project\03_Source_To_Target_Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5042A39B-4C71-44E0-8B64-E9B40D506C59}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5284189B-B133-48FA-8B46-6F0BFE285B8E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{AFC18C71-006C-45EF-A29B-E9C1990AEBB0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="41">
   <si>
     <t>Source Column</t>
   </si>
@@ -109,6 +109,45 @@
   </si>
   <si>
     <t>Satandardize state names</t>
+  </si>
+  <si>
+    <t>GENDER</t>
+  </si>
+  <si>
+    <t>DATE_OF_BIRTH</t>
+  </si>
+  <si>
+    <t>COUNTRY</t>
+  </si>
+  <si>
+    <t>CREATED_DATE</t>
+  </si>
+  <si>
+    <t>UPDATED_DATE</t>
+  </si>
+  <si>
+    <t>INITCAP(TRIM(GENDER))</t>
+  </si>
+  <si>
+    <t>Allowed values: Male, Female, Other</t>
+  </si>
+  <si>
+    <t>Cannot be a future date</t>
+  </si>
+  <si>
+    <t>No Transformations</t>
+  </si>
+  <si>
+    <t>UPPER(TRIM(COUNTRY))</t>
+  </si>
+  <si>
+    <t>Satandardize country names</t>
+  </si>
+  <si>
+    <t>Preserve source value</t>
+  </si>
+  <si>
+    <t>Used for latest record selection</t>
   </si>
 </sst>
 </file>
@@ -470,13 +509,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B3A8007-9D67-494A-A591-D67ED52EE07F}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.36328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37.1796875" bestFit="1" customWidth="1"/>
   </cols>
@@ -606,19 +645,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -626,19 +665,119 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E10" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/03_Source_To_Target_Mapping/RetailMart_STM.xlsx
+++ b/03_Source_To_Target_Mapping/RetailMart_STM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub_Projects\Retail_DWH_Project\03_Source_To_Target_Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5284189B-B133-48FA-8B46-6F0BFE285B8E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029656F4-0A53-4D1D-8267-98BC5D14B21C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{AFC18C71-006C-45EF-A29B-E9C1990AEBB0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="43">
   <si>
     <t>Source Column</t>
   </si>
@@ -148,6 +148,12 @@
   </si>
   <si>
     <t>Used for latest record selection</t>
+  </si>
+  <si>
+    <t>CUSTOMER_STATUS</t>
+  </si>
+  <si>
+    <t>Must be active or inactive</t>
   </si>
 </sst>
 </file>
@@ -509,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B3A8007-9D67-494A-A591-D67ED52EE07F}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.36328125" bestFit="1" customWidth="1"/>
@@ -745,19 +751,19 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E12" t="s">
         <v>36</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -765,18 +771,38 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E13" t="s">
         <v>36</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>40</v>
       </c>
     </row>

--- a/03_Source_To_Target_Mapping/RetailMart_STM.xlsx
+++ b/03_Source_To_Target_Mapping/RetailMart_STM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub_Projects\Retail_DWH_Project\03_Source_To_Target_Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029656F4-0A53-4D1D-8267-98BC5D14B21C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB14F73C-E76C-4079-A463-8AD2529BB673}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{AFC18C71-006C-45EF-A29B-E9C1990AEBB0}"/>
   </bookViews>

--- a/03_Source_To_Target_Mapping/RetailMart_STM.xlsx
+++ b/03_Source_To_Target_Mapping/RetailMart_STM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub_Projects\Retail_DWH_Project\03_Source_To_Target_Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB14F73C-E76C-4079-A463-8AD2529BB673}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6AC5D7B-0183-4CA1-AF57-8F8E7BFFD6FA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{AFC18C71-006C-45EF-A29B-E9C1990AEBB0}"/>
   </bookViews>

--- a/03_Source_To_Target_Mapping/RetailMart_STM.xlsx
+++ b/03_Source_To_Target_Mapping/RetailMart_STM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub_Projects\Retail_DWH_Project\03_Source_To_Target_Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6AC5D7B-0183-4CA1-AF57-8F8E7BFFD6FA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BC5528-1907-4C8A-9247-E558A3347EF9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{AFC18C71-006C-45EF-A29B-E9C1990AEBB0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="44">
   <si>
     <t>Source Column</t>
   </si>
@@ -154,6 +154,9 @@
   </si>
   <si>
     <t>Must be active or inactive</t>
+  </si>
+  <si>
+    <t>UPPER(TRIM(CUSTOMER_STATUS))</t>
   </si>
 </sst>
 </file>
@@ -519,10 +522,10 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="37.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -760,7 +763,7 @@
         <v>41</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>42</v>
